--- a/TestCases_Docs/Register_Tcs.xlsx
+++ b/TestCases_Docs/Register_Tcs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yasse\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yasse\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E65E55A-289A-44F7-8AB8-981A39BC9533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49D4A68-D930-46FF-8073-44213A80986A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="362">
   <si>
     <t>TesTCASE ID</t>
   </si>
@@ -1760,6 +1760,10 @@
   <si>
     <t>SIQ_Acc_09</t>
   </si>
+  <si>
+    <t xml:space="preserve">
+SRS-FN-REGISTER-007</t>
+  </si>
 </sst>
 </file>
 
@@ -2365,22 +2369,6 @@
       </fill>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF6F8F9"/>
@@ -2404,13 +2392,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="18">
     <tableStyle name="Register_Tcs-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="34"/>
-      <tableStyleElement type="headerRow" dxfId="37"/>
-      <tableStyleElement type="firstRowStripe" dxfId="36"/>
-      <tableStyleElement type="secondRowStripe" dxfId="35"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="37"/>
+      <tableStyleElement type="headerRow" dxfId="36"/>
+      <tableStyleElement type="firstRowStripe" dxfId="35"/>
+      <tableStyleElement type="secondRowStripe" dxfId="34"/>
     </tableStyle>
     <tableStyle name="Register_Tcs-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="firstRowStripe" dxfId="33"/>
@@ -3133,8 +3137,8 @@
       <c r="K6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="4" t="s">
-        <v>47</v>
+      <c r="L6" s="5" t="s">
+        <v>361</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>26</v>
